--- a/data/trans_orig/P05A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225239</t>
+          <t>225292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268721</t>
+          <t>267862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223386</t>
+          <t>225530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263177</t>
+          <t>265803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>463673</t>
+          <t>459355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>521326</t>
+          <t>518293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135301</t>
+          <t>136305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>178563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121184</t>
+          <t>118479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157850</t>
+          <t>158113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268306</t>
+          <t>267000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322255</t>
+          <t>322684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78731</t>
+          <t>80084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113488</t>
+          <t>112743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349165</t>
+          <t>351138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403859</t>
+          <t>404050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299221</t>
+          <t>298876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348169</t>
+          <t>348018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665834</t>
+          <t>665611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736393</t>
+          <t>739083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>192994</t>
+          <t>193506</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245247</t>
+          <t>242141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176018</t>
+          <t>175145</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>221987</t>
+          <t>224068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>382043</t>
+          <t>381944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>446048</t>
+          <t>450444</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109343</t>
+          <t>108563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71278</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105997</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152144</t>
+          <t>152357</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204169</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342411</t>
+          <t>343320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393893</t>
+          <t>393862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>345827</t>
+          <t>346537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>398265</t>
+          <t>401248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>702997</t>
+          <t>704458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>780323</t>
+          <t>777802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216796</t>
+          <t>216173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>264906</t>
+          <t>266133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208140</t>
+          <t>208538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255931</t>
+          <t>260167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435685</t>
+          <t>438959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509271</t>
+          <t>512436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86527</t>
+          <t>88796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119888</t>
+          <t>120055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149388</t>
+          <t>146013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198427</t>
+          <t>194929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288143</t>
+          <t>287830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339004</t>
+          <t>339503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290156</t>
+          <t>290828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340581</t>
+          <t>343241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591843</t>
+          <t>591641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>666445</t>
+          <t>663675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188135</t>
+          <t>188639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237157</t>
+          <t>238780</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189586</t>
+          <t>191024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>241227</t>
+          <t>239189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392289</t>
+          <t>394249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462416</t>
+          <t>464747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71699</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108240</t>
+          <t>107415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>63960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99872</t>
+          <t>99985</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143710</t>
+          <t>145272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195684</t>
+          <t>196216</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197511</t>
+          <t>197081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240989</t>
+          <t>239624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>196492</t>
+          <t>200420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241229</t>
+          <t>243299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409881</t>
+          <t>409107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>474402</t>
+          <t>468940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133175</t>
+          <t>133513</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>175286</t>
+          <t>173564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145460</t>
+          <t>142414</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185349</t>
+          <t>184391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>286188</t>
+          <t>287916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>346455</t>
+          <t>347193</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71511</t>
+          <t>70877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45274</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97966</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137798</t>
+          <t>137741</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124195</t>
+          <t>126455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163125</t>
+          <t>162760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160868</t>
+          <t>162817</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200201</t>
+          <t>199538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>298967</t>
+          <t>297509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>351201</t>
+          <t>351479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>100734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134434</t>
+          <t>136344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>114988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151125</t>
+          <t>151599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>225385</t>
+          <t>225190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277197</t>
+          <t>278991</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64737</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52844</t>
+          <t>53143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>69771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>107172</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144360</t>
+          <t>144452</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>158404</t>
+          <t>160785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>200117</t>
+          <t>200871</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>278786</t>
+          <t>282755</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332650</t>
+          <t>334328</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108542</t>
+          <t>107180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116950</t>
+          <t>117682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154626</t>
+          <t>157231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205639</t>
+          <t>205017</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>255919</t>
+          <t>255015</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41058</t>
+          <t>40981</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87335</t>
+          <t>86272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82144</t>
+          <t>81965</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>118040</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1743116</t>
+          <t>1729135</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1858701</t>
+          <t>1849140</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1778080</t>
+          <t>1780728</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1901421</t>
+          <t>1899873</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3552114</t>
+          <t>3552897</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3721761</t>
+          <t>3722514</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1133805</t>
+          <t>1132119</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1245132</t>
+          <t>1247293</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1159305</t>
+          <t>1157912</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1278472</t>
+          <t>1273602</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2330850</t>
+          <t>2328104</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2489938</t>
+          <t>2487926</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>392611</t>
+          <t>394468</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>476508</t>
+          <t>472340</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>443808</t>
+          <t>447356</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>528677</t>
+          <t>530518</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>861559</t>
+          <t>862966</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>978613</t>
+          <t>976599</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>263631</t>
+          <t>264770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304745</t>
+          <t>303333</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248387</t>
+          <t>247917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285161</t>
+          <t>285640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>523329</t>
+          <t>523856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577758</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>82762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118602</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71527</t>
+          <t>71051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104022</t>
+          <t>104046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164204</t>
+          <t>163837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211247</t>
+          <t>211141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>47115</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>60736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91642</t>
+          <t>91965</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340251</t>
+          <t>337859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386534</t>
+          <t>384897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334944</t>
+          <t>331479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379756</t>
+          <t>377468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686687</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751779</t>
+          <t>756303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>139794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>184618</t>
+          <t>184468</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119776</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157798</t>
+          <t>159489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270337</t>
+          <t>270724</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>330816</t>
+          <t>330039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>81516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53751</t>
+          <t>53537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82582</t>
+          <t>84966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111883</t>
+          <t>111795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153735</t>
+          <t>154695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>414767</t>
+          <t>413288</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465185</t>
+          <t>463220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>427886</t>
+          <t>425819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>474666</t>
+          <t>473119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>853701</t>
+          <t>853559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>922226</t>
+          <t>921767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138097</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185528</t>
+          <t>186569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121808</t>
+          <t>121379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162441</t>
+          <t>163233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275997</t>
+          <t>275430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336725</t>
+          <t>336697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82751</t>
+          <t>80724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82257</t>
+          <t>82001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106123</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151698</t>
+          <t>152255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>397515</t>
+          <t>393565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445541</t>
+          <t>445315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>411169</t>
+          <t>410169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>457900</t>
+          <t>458485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822902</t>
+          <t>822942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>893060</t>
+          <t>890970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137303</t>
+          <t>138533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180969</t>
+          <t>186100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116523</t>
+          <t>117364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159230</t>
+          <t>159051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265193</t>
+          <t>268524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329070</t>
+          <t>329897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77801</t>
+          <t>80595</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58360</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91935</t>
+          <t>91211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114992</t>
+          <t>112662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161104</t>
+          <t>158147</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286312</t>
+          <t>287281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330822</t>
+          <t>332195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>283492</t>
+          <t>285060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330141</t>
+          <t>330156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>588606</t>
+          <t>585806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>650065</t>
+          <t>649977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89874</t>
+          <t>89823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128791</t>
+          <t>128860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94394</t>
+          <t>95898</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>132931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>197990</t>
+          <t>197327</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>250902</t>
+          <t>252105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54600</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89215</t>
+          <t>89253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>105157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149219</t>
+          <t>152379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207101</t>
+          <t>209309</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>208807</t>
+          <t>209508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246682</t>
+          <t>246675</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>431047</t>
+          <t>429425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>482042</t>
+          <t>481329</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59511</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90940</t>
+          <t>88394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>72866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108865</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>141125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186552</t>
+          <t>187790</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69290</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69701</t>
+          <t>70288</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105491</t>
+          <t>104372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148729</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176164</t>
+          <t>173742</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>239925</t>
+          <t>240687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>282039</t>
+          <t>282408</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>397105</t>
+          <t>397829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>449428</t>
+          <t>452331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58065</t>
+          <t>58778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83588</t>
+          <t>85538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>80486</t>
+          <t>79717</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119705</t>
+          <t>118550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143645</t>
+          <t>143974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>191133</t>
+          <t>190193</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25645</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80165</t>
+          <t>80502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2151544</t>
+          <t>2159371</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2265633</t>
+          <t>2269493</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2249527</t>
+          <t>2252318</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2360649</t>
+          <t>2362044</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4437544</t>
+          <t>4441809</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4592643</t>
+          <t>4598625</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>783868</t>
+          <t>779793</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>884938</t>
+          <t>883661</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>759569</t>
+          <t>756270</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>856330</t>
+          <t>862783</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1573943</t>
+          <t>1569334</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1711338</t>
+          <t>1719785</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>371894</t>
+          <t>374471</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>453696</t>
+          <t>450897</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>689472</t>
+          <t>697281</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>799951</t>
+          <t>804012</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282380</t>
+          <t>281127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335619</t>
+          <t>336572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182111</t>
+          <t>181967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225684</t>
+          <t>227356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>475451</t>
+          <t>477743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>550476</t>
+          <t>549017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41210</t>
+          <t>40505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84890</t>
+          <t>88500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>49749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>89296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98973</t>
+          <t>101607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157399</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48123</t>
+          <t>51601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60334</t>
+          <t>62941</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96924</t>
+          <t>97787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284351</t>
+          <t>288500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>334402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383331</t>
+          <t>385121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448366</t>
+          <t>445873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>684317</t>
+          <t>683348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>772045</t>
+          <t>769773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57831</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99375</t>
+          <t>96234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81108</t>
+          <t>83238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103575</t>
+          <t>103297</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165602</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>55051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>24053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56747</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100037</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>377896</t>
+          <t>376164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>421985</t>
+          <t>418404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>428674</t>
+          <t>429256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>485105</t>
+          <t>486800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>818560</t>
+          <t>818067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>896070</t>
+          <t>889865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66112</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103422</t>
+          <t>101394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>64662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105436</t>
+          <t>106266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144145</t>
+          <t>144060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200311</t>
+          <t>195430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69266</t>
+          <t>68336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65160</t>
+          <t>65619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84036</t>
+          <t>83336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123394</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>620050</t>
+          <t>616728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>804757</t>
+          <t>811695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>506948</t>
+          <t>505477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>556185</t>
+          <t>554858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1147227</t>
+          <t>1147125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1381818</t>
+          <t>1389007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162717</t>
+          <t>163662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129593</t>
+          <t>128858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125948</t>
+          <t>134267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274829</t>
+          <t>274715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111691</t>
+          <t>111047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60432</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89387</t>
+          <t>88655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88641</t>
+          <t>83755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184612</t>
+          <t>187530</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>405207</t>
+          <t>405065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>443631</t>
+          <t>442450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>391837</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>421247</t>
+          <t>419646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>805918</t>
+          <t>806177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854748</t>
+          <t>854825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>71977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>105710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67657</t>
+          <t>68042</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93414</t>
+          <t>93066</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>148214</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189269</t>
+          <t>189413</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38341</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61498</t>
+          <t>62855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>51834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71954</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96181</t>
+          <t>96215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>128654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>256568</t>
+          <t>255656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283847</t>
+          <t>283412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>445067</t>
+          <t>445999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>563917</t>
+          <t>561908</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>714064</t>
+          <t>714079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>866819</t>
+          <t>872064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55883</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>112189</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10956,17 +10956,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>137256</t>
+          <t>137255</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>71142</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181210</t>
+          <t>181010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41299</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85586</t>
+          <t>87493</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>184822</t>
+          <t>185428</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208200</t>
+          <t>207524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>302276</t>
+          <t>302427</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>329235</t>
+          <t>328718</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>493440</t>
+          <t>495606</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>529945</t>
+          <t>530057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>54811</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76141</t>
+          <t>75957</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,49 +11362,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>69866</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>58526</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>80741</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>18,98%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>69866</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>59877</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>82562</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>246</t>
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>120707</t>
+          <t>119640</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>150439</t>
+          <t>149887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>49311</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50565</t>
+          <t>50520</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72766</t>
+          <t>71587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2530324</t>
+          <t>2525983</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2834062</t>
+          <t>2794662</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2735857</t>
+          <t>2738428</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2982235</t>
+          <t>2968838</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5299365</t>
+          <t>5297229</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5651024</t>
+          <t>5674132</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>425937</t>
+          <t>434912</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>608139</t>
+          <t>616424</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,47 +11818,47 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>551521</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>457222</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>608826</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
           <t>12,32%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>551521</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>451294</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>609064</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>962630</t>
+          <t>945318</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1195153</t>
+          <t>1198308</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>228693</t>
+          <t>225212</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>340665</t>
+          <t>337701</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>275689</t>
+          <t>278067</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>383117</t>
+          <t>381928</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>552304</t>
+          <t>550355</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>705616</t>
+          <t>698791</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225292</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>267862</t>
+          <t>267694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225530</t>
+          <t>224132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265803</t>
+          <t>264074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459355</t>
+          <t>460914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>518293</t>
+          <t>520393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136305</t>
+          <t>136889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178563</t>
+          <t>176291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118479</t>
+          <t>119558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158113</t>
+          <t>157585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267000</t>
+          <t>268534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322684</t>
+          <t>322934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64996</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>34337</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59420</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80084</t>
+          <t>79627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112743</t>
+          <t>115834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351138</t>
+          <t>347925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404050</t>
+          <t>403330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>298876</t>
+          <t>299381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348018</t>
+          <t>351228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665611</t>
+          <t>667221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>739083</t>
+          <t>735542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>193506</t>
+          <t>194148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>245388</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175145</t>
+          <t>175058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224068</t>
+          <t>222635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>381944</t>
+          <t>382186</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>450444</t>
+          <t>451680</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71776</t>
+          <t>71978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108563</t>
+          <t>110786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>71201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108150</t>
+          <t>107018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152357</t>
+          <t>153107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204442</t>
+          <t>204418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>343320</t>
+          <t>341525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393862</t>
+          <t>392440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>346537</t>
+          <t>344285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>401248</t>
+          <t>399907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>704458</t>
+          <t>702051</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>777802</t>
+          <t>779948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216173</t>
+          <t>217821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>268261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208538</t>
+          <t>207446</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260167</t>
+          <t>258833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438959</t>
+          <t>435389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512436</t>
+          <t>512042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>57543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88796</t>
+          <t>87957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83166</t>
+          <t>83470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120055</t>
+          <t>120484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146013</t>
+          <t>147347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194929</t>
+          <t>197356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>287830</t>
+          <t>286116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339503</t>
+          <t>340198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290828</t>
+          <t>289958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343241</t>
+          <t>343891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591641</t>
+          <t>591594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>663675</t>
+          <t>665456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188639</t>
+          <t>188632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238780</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191024</t>
+          <t>190767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239189</t>
+          <t>241492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394249</t>
+          <t>392857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>464747</t>
+          <t>464225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70949</t>
+          <t>71783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>106788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63960</t>
+          <t>64147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99985</t>
+          <t>99914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145272</t>
+          <t>146140</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196216</t>
+          <t>196847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197081</t>
+          <t>198048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239624</t>
+          <t>240223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200420</t>
+          <t>199617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243299</t>
+          <t>242460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409107</t>
+          <t>408209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468940</t>
+          <t>468901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133513</t>
+          <t>131836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>174175</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142414</t>
+          <t>143148</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>184391</t>
+          <t>183515</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>287916</t>
+          <t>288759</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>347193</t>
+          <t>350649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43259</t>
+          <t>42845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>71734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>45774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>76581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96380</t>
+          <t>97792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137741</t>
+          <t>138701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126455</t>
+          <t>127034</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>162760</t>
+          <t>162622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162817</t>
+          <t>161104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>199538</t>
+          <t>199265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>297509</t>
+          <t>297365</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>351479</t>
+          <t>350780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100734</t>
+          <t>101309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136344</t>
+          <t>137694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114988</t>
+          <t>116436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151599</t>
+          <t>152024</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>225190</t>
+          <t>226014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278991</t>
+          <t>276230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>34757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62557</t>
+          <t>63467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>70592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108169</t>
+          <t>108000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111324</t>
+          <t>110244</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144452</t>
+          <t>144096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>160785</t>
+          <t>157905</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>200871</t>
+          <t>201250</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>282755</t>
+          <t>283442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>334328</t>
+          <t>335925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>76678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107180</t>
+          <t>109699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>117682</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157231</t>
+          <t>159099</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205017</t>
+          <t>203381</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>255015</t>
+          <t>254000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>41732</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>55343</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86272</t>
+          <t>86656</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>81965</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>118040</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1729135</t>
+          <t>1738050</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1849140</t>
+          <t>1854928</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1780728</t>
+          <t>1772456</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1899873</t>
+          <t>1896145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3552897</t>
+          <t>3548327</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3722514</t>
+          <t>3729371</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1132119</t>
+          <t>1137479</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1247293</t>
+          <t>1249172</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1157912</t>
+          <t>1165054</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1273602</t>
+          <t>1284296</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2328104</t>
+          <t>2326407</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2487926</t>
+          <t>2489037</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>394468</t>
+          <t>395748</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>472340</t>
+          <t>473596</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>447356</t>
+          <t>442789</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>530518</t>
+          <t>529264</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>862966</t>
+          <t>856591</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>976599</t>
+          <t>976967</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>264770</t>
+          <t>263484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>303333</t>
+          <t>300418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247917</t>
+          <t>247836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285640</t>
+          <t>284633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>523856</t>
+          <t>523259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574403</t>
+          <t>577328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82762</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119016</t>
+          <t>119929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71051</t>
+          <t>70439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104046</t>
+          <t>102841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163837</t>
+          <t>164244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211141</t>
+          <t>212654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>48253</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60736</t>
+          <t>58285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91965</t>
+          <t>92820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337859</t>
+          <t>340416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>384897</t>
+          <t>386097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331479</t>
+          <t>334935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377468</t>
+          <t>377505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687969</t>
+          <t>687692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>756303</t>
+          <t>754475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>139794</t>
+          <t>140643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>184468</t>
+          <t>183127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120444</t>
+          <t>120899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>159489</t>
+          <t>159310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270724</t>
+          <t>270358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>330039</t>
+          <t>331137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>50438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81516</t>
+          <t>80949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53537</t>
+          <t>54163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>83888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111795</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154695</t>
+          <t>155234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>413288</t>
+          <t>415085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463220</t>
+          <t>464670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425819</t>
+          <t>427572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>473119</t>
+          <t>477281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>853559</t>
+          <t>853817</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>921767</t>
+          <t>923337</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140982</t>
+          <t>139624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186569</t>
+          <t>184397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121379</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163233</t>
+          <t>162744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275430</t>
+          <t>274500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336697</t>
+          <t>334699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80724</t>
+          <t>81784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>51042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82001</t>
+          <t>81442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109829</t>
+          <t>109219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>152493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>393565</t>
+          <t>397436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445315</t>
+          <t>447562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>410169</t>
+          <t>407740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>458485</t>
+          <t>457415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822942</t>
+          <t>823585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>890970</t>
+          <t>890651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138533</t>
+          <t>136053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186100</t>
+          <t>183419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117364</t>
+          <t>117134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159051</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268524</t>
+          <t>267449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329897</t>
+          <t>328218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48529</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80595</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57396</t>
+          <t>58851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91211</t>
+          <t>90998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112662</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158147</t>
+          <t>160071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287281</t>
+          <t>286473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332195</t>
+          <t>331182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>285060</t>
+          <t>286614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330156</t>
+          <t>329606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>585806</t>
+          <t>586690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>649977</t>
+          <t>647069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128860</t>
+          <t>129114</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95898</t>
+          <t>95384</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132931</t>
+          <t>133044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>197327</t>
+          <t>196046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>252105</t>
+          <t>251772</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>54988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89253</t>
+          <t>88662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105157</t>
+          <t>104920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152379</t>
+          <t>149063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209309</t>
+          <t>208792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242914</t>
+          <t>244959</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>209508</t>
+          <t>207960</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246675</t>
+          <t>246894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>429425</t>
+          <t>430775</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>481329</t>
+          <t>483148</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59083</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72866</t>
+          <t>75924</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106687</t>
+          <t>110803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141125</t>
+          <t>141554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187790</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40826</t>
+          <t>41311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>69510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70288</t>
+          <t>70367</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>104372</t>
+          <t>105113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>148242</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>173742</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240687</t>
+          <t>238846</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>282408</t>
+          <t>282430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>397829</t>
+          <t>396657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>452331</t>
+          <t>447716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85538</t>
+          <t>84520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79717</t>
+          <t>79508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118550</t>
+          <t>118035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143974</t>
+          <t>146044</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190193</t>
+          <t>193040</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16430</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33051</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>55051</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80502</t>
+          <t>79665</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2159371</t>
+          <t>2147596</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2269493</t>
+          <t>2263126</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2252318</t>
+          <t>2251117</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2362044</t>
+          <t>2362695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4441809</t>
+          <t>4436786</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4598625</t>
+          <t>4601005</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>779793</t>
+          <t>788597</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>883661</t>
+          <t>886888</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>756270</t>
+          <t>757766</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>862783</t>
+          <t>856451</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1569334</t>
+          <t>1567552</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1719785</t>
+          <t>1718443</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>302935</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>370654</t>
+          <t>373656</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>450897</t>
+          <t>455926</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>697281</t>
+          <t>693249</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>804012</t>
+          <t>800437</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>311069</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>281127</t>
+          <t>281197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>336572</t>
+          <t>334987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8528,32 +8528,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>203933</t>
+          <t>235062</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181967</t>
+          <t>209586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227356</t>
+          <t>259926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>515283</t>
+          <t>546131</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>477743</t>
+          <t>503715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>549017</t>
+          <t>583206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -8606,32 +8606,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60649</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40505</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88500</t>
+          <t>92029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8641,32 +8641,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67046</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49749</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89296</t>
+          <t>98521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8676,32 +8676,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>127695</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101607</t>
+          <t>113487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158893</t>
+          <t>177841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -8719,32 +8719,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51601</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8754,32 +8754,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>48872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>71371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8789,32 +8789,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>77376</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48194</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97787</t>
+          <t>105801</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8832,17 +8832,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8867,17 +8867,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313036</t>
+          <t>360110</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313036</t>
+          <t>360110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313036</t>
+          <t>360110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713023</t>
+          <t>767903</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713023</t>
+          <t>767903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713023</t>
+          <t>767903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8949,32 +8949,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311993</t>
+          <t>346655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288500</t>
+          <t>321944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334402</t>
+          <t>371451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>409240</t>
+          <t>383922</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385121</t>
+          <t>362707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445873</t>
+          <t>403927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9019,32 +9019,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>721233</t>
+          <t>730578</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683348</t>
+          <t>692968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769773</t>
+          <t>759737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -9062,32 +9062,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74731</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56480</t>
+          <t>64670</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96234</t>
+          <t>106751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9097,32 +9097,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62780</t>
+          <t>74969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83238</t>
+          <t>93536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9132,32 +9132,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>160879</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>135466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>191668</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -9175,32 +9175,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55051</t>
+          <t>63363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9210,32 +9210,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55116</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9245,32 +9245,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76896</t>
+          <t>87166</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55510</t>
+          <t>68421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>111234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9405,32 +9405,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>399126</t>
+          <t>462430</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>376164</t>
+          <t>437821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>418404</t>
+          <t>483345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>451030</t>
+          <t>456304</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>429256</t>
+          <t>437870</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>486800</t>
+          <t>473327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9475,32 +9475,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>850157</t>
+          <t>918734</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>818067</t>
+          <t>888470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>889865</t>
+          <t>946430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -9518,32 +9518,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82854</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>77870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101394</t>
+          <t>115424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88436</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64662</t>
+          <t>87642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>120862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9588,32 +9588,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>171290</t>
+          <t>196698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144060</t>
+          <t>174303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195430</t>
+          <t>222474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -9631,32 +9631,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>60287</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>45499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68336</t>
+          <t>75513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>64182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65619</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9701,32 +9701,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>124470</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83336</t>
+          <t>104586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124668</t>
+          <t>144459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -9744,17 +9744,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9814,17 +9814,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1126263</t>
+          <t>1239902</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>701116</t>
+          <t>492159</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>616728</t>
+          <t>467177</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>811695</t>
+          <t>514685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>526174</t>
+          <t>531580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>505477</t>
+          <t>512062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554858</t>
+          <t>551528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9931,32 +9931,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1227291</t>
+          <t>1023740</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1147125</t>
+          <t>989681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1389007</t>
+          <t>1055376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -9974,32 +9974,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>111874</t>
+          <t>124525</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47185</t>
+          <t>105012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163662</t>
+          <t>146413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10009,32 +10009,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>111630</t>
+          <t>122971</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>107593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>140642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10044,32 +10044,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>223505</t>
+          <t>247496</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134267</t>
+          <t>223299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274715</t>
+          <t>273577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74795</t>
+          <t>83933</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>66113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111047</t>
+          <t>101511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>81626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88655</t>
+          <t>95327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10157,32 +10157,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>149711</t>
+          <t>165559</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83755</t>
+          <t>144415</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>187530</t>
+          <t>190430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -10200,17 +10200,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736177</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736177</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712721</t>
+          <t>736177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10270,17 +10270,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600507</t>
+          <t>1436795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10317,32 +10317,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>424641</t>
+          <t>461159</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>405065</t>
+          <t>439835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>442450</t>
+          <t>479799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10352,32 +10352,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>405448</t>
+          <t>448828</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>389612</t>
+          <t>432311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>419646</t>
+          <t>465043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10387,32 +10387,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>830089</t>
+          <t>909987</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>806177</t>
+          <t>884612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854825</t>
+          <t>934501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -10430,32 +10430,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87677</t>
+          <t>96140</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71977</t>
+          <t>79074</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105710</t>
+          <t>113827</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10465,17 +10465,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>89513</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>76200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93066</t>
+          <t>103356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10500,32 +10500,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>168220</t>
+          <t>185653</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148214</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189413</t>
+          <t>209424</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -10543,32 +10543,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>40583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>65688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10578,32 +10578,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>69829</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51834</t>
+          <t>58036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73631</t>
+          <t>82687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10613,32 +10613,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>110217</t>
+          <t>121877</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96215</t>
+          <t>105761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128654</t>
+          <t>141545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10656,17 +10656,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10773,32 +10773,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>270751</t>
+          <t>300812</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255656</t>
+          <t>285790</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283412</t>
+          <t>314844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10808,32 +10808,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>504542</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>445999</t>
+          <t>309582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>561908</t>
+          <t>337766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>775293</t>
+          <t>624666</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>714079</t>
+          <t>603638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>872064</t>
+          <t>643373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -10886,32 +10886,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>66037</t>
+          <t>72224</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55264</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78419</t>
+          <t>85903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10921,32 +10921,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>71219</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>91280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>137255</t>
+          <t>151296</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71142</t>
+          <t>134204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181010</t>
+          <t>168735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -10999,32 +10999,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40868</t>
+          <t>44856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11034,32 +11034,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53205</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11069,32 +11069,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>63984</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>59143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87493</t>
+          <t>83581</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -11112,17 +11112,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11147,17 +11147,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11182,17 +11182,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11229,32 +11229,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>196438</t>
+          <t>215045</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>185428</t>
+          <t>199583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207524</t>
+          <t>227387</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11264,32 +11264,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>316163</t>
+          <t>344245</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>302427</t>
+          <t>329000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>328718</t>
+          <t>357243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11299,32 +11299,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>512601</t>
+          <t>559291</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>495606</t>
+          <t>539673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>530057</t>
+          <t>579007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -11342,32 +11342,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>64355</t>
+          <t>71199</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>60234</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75957</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11377,32 +11377,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>69866</t>
+          <t>76872</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58526</t>
+          <t>66205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80741</t>
+          <t>89207</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11412,32 +11412,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>134221</t>
+          <t>148071</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119640</t>
+          <t>131937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>164586</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -11455,32 +11455,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>31947</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11490,32 +11490,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>42899</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11525,32 +11525,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>60699</t>
+          <t>66300</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>55193</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71587</t>
+          <t>79565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -11568,17 +11568,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282221</t>
+          <t>309645</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282221</t>
+          <t>309645</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282221</t>
+          <t>309645</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11603,17 +11603,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425300</t>
+          <t>464016</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425300</t>
+          <t>464016</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425300</t>
+          <t>464016</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11638,17 +11638,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707521</t>
+          <t>773662</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707521</t>
+          <t>773662</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707521</t>
+          <t>773662</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11685,32 +11685,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2615415</t>
+          <t>2589330</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2525983</t>
+          <t>2536045</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2794662</t>
+          <t>2650710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11720,32 +11720,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2816531</t>
+          <t>2723796</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2738428</t>
+          <t>2672448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2968838</t>
+          <t>2773821</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11755,32 +11755,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5431947</t>
+          <t>5313125</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5297229</t>
+          <t>5235967</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5674132</t>
+          <t>5390941</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -11798,32 +11798,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>548176</t>
+          <t>612957</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>434912</t>
+          <t>568661</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>616424</t>
+          <t>662512</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11833,32 +11833,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>551521</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>457222</t>
+          <t>580140</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>661974</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11868,32 +11868,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1099697</t>
+          <t>1234490</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>945318</t>
+          <t>1171461</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1198308</t>
+          <t>1293907</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -11911,32 +11911,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>294339</t>
+          <t>326541</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>225212</t>
+          <t>293368</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>337701</t>
+          <t>371754</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11946,32 +11946,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>342031</t>
+          <t>386490</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>278067</t>
+          <t>352469</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>381928</t>
+          <t>425390</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11981,32 +11981,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>636370</t>
+          <t>713031</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>550355</t>
+          <t>660668</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>698791</t>
+          <t>764531</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12059,17 +12059,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12094,17 +12094,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
